--- a/datos/indicadores_nacionales_razones_lalo_V5.xlsx
+++ b/datos/indicadores_nacionales_razones_lalo_V5.xlsx
@@ -1,1160 +1,1189 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SIGEH\Desktop\Lalo\Gob\Proyectos\Tablero_Indicadores\datos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AADBB8-2488-45E4-9968-B3B2FFBBDA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="378">
-  <si>
-    <t xml:space="preserve">Tema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descripción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En razón de algo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">temporalidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Económico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aves. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la Producción de aves.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miles de pesos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Más es mejor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Agricultura y Desarrollo Rural SADER. Servicio de Información Agroalimentaria y Pesquera SIAP. Producción Ganadera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aves. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de aves.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toneladas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cera. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la producción de cera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cera. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de cera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crecimiento Economico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se refiere al incremento en la producción de bienes y servicios en una economía de un periodo a otro.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talvez porcentaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trimestral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">México ¿Cómo vamos?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuartos de Hospedaje según categoría (1 estrella)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de cuartos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. México en Cifras. Tabulados de Integración. Turismo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuartos de Hospedaje según categoría (2 estrellas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuartos de Hospedaje según categoría (3 estrellas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuartos de Hospedaje según categoría (4 estrellas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuartos de Hospedaje según categoría (5 estrellas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuartos de Hospedaje según categoría (sin categoría)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuartos de establecimientos de Hospedaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor absoluto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desigualdad Laboral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La desigualdad laboral se manifiesta en la brecha de género, la informalidad y la brecha salarial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talvez coeficiente de Gini entre 0 y 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menos es mejor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deuda Pública (Porcentaje del PIB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compara la variación anual de la deuda neta del sector público federal con la variación anual del PIB a precios corrientes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empleos formales generados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refleja el número de puestos de trabajo formales creados o eliminados en el registro del IMSS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de puestos de trabajo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Establecimiento de Hospedaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Establecimiento de Hospedaje según categoría (1 estrella)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de establecimientos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Establecimiento de Hospedaje según categoría (2 estrellas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Establecimiento de Hospedaje según categoría (3 estrellas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Establecimiento de Hospedaje según categoría (4 estrellas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Establecimiento de Hospedaje según categoría (5 estrellas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Establecimientos de Hospedaje según categoría (sin categoría)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exportaciones por Entidad Federativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Información referente al valor de las exportaciones de mercancías por entidad federativa, que permite conocer la participación de cada una de ellas en el intercambio comercial que realiza México con el resto del mundo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millones de dólares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganado Bovino. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la Producción de ganado bovino en pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganado Bovino. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de ganado bovino en pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganado Caprino. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la Producción de ganado caprino en pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganado Caprino. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de ganado caprino en pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganado Ovino. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la Producción de ganado ovino en pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganado Ovino. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de ganado ovino en pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganado Porcino. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la Producción de ganado porcino en pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganado Porcino. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de ganado porcino en pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gasto corriente promedio trimestral por hogar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gasto corriente promedio trimestral en los hogares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pesos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bianual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. Encuesta Nacional de Ingreso Gasto en los Hogares ENIGH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guajolotes. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la Producción de guajolotes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guajolotes. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de guajolotes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huevo para Plato. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la producción de huevo para plato.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huevo para plato. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de huevo para plato.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicador Mensual de la Actividad Industrial por Entidad Federativa IMAIEF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proporciona información estadística de corto plazo en el ámbito estatal que permite dar seguimiento al comportamiento de las actividades secundarias en los estados.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicador Trimestral de la Actividad Economica Estatal ITAEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ofrece un panorama sobre la evolución económica de las entidades federativas del país.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informalidad Laboral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proporción de la población ocupada que son laboralmente vulnerables por la naturaleza de la unidad económica para la que trabajan, así como aquellas personas ocupadas cuyo vínculo laboral no es reconocido por su fuente de trabajo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos por cada 100 mil habitantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingreso corriente promedio trimestral por hogar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se compone del ingreso corriente total y de las percepciones financieras y de capital.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. Encuesta Nacional de Ingresos y Gastos de los Hogares (ENIGH).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingresos por Remesas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los ingresos por remesas son el dinero que envían los trabajadores migrantes a sus familias en sus países de origen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco de México</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inversion Extranjera Directa IED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es la suma de los capitales a largo plazo que provienen de otros países y entran a México para la creación de empresas agrícolas, industriales y de servicios. El término clave es “largo plazo”, ya que esto es lo que la separa de cualquier otro flujo de capital extranjero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Economía</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lana. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la producción de lana.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lana. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de lana.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leche de Bovino. Valor de la Producción miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la producción de leche de bovino.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leche de Bovino. Volumen de la Producción (miles de litros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de leche de bovino.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miles de litros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leche de Caprino. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la producción de leche de ganado caprino.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leche de Caprino. Volumen de la Producción (miles de litros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de leche de ganado caprino.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llegada de Turistas Totales a la Entidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llegada de Turistas a la Entidad por Tipo de Turismo (extranjeros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llegada de Turistas a la Entidad por Tipo de Turismo (nacionales)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitud de la Red Carretera Federal (kilometros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registra el total de kilómetros de la red carretera federal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilometros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. México en Cifras. Tabulados de Integración. Transporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitud de la Red de Alimentadoras estatales (kilometros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registra el total de kilómetros de la red de carreteras alimentadoras estatales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitud de la Red de Brechas Mejoradas (kilometros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registra el total de kilómetros de brechas mejoradas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitud de la Red de Caminos Rurales (kilometros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registra el total de kilómetros de la red de caminos rurales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miel. Valor de la Producción (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la producción de miel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miel. Volumen de la Producción (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción de miel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oferta de alojamiento en la entidad (cuartos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponibilidad de cuartos en los establecimientos de alojamiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Turismo. DataTur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una patente es un derecho exclusivo que concede el Estado para la protección de una invención, la que proporciona derechos exclusivos que permitirán utilizar y explotar su invención e impedir que terceros la utilicen sin su consentimiento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de patentes registradas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Mexicano de la Pro´piedad Industrial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población Desocupada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se refiere a personas que no tienen un trabajo pero están activamente buscando uno y están disponibles para trabajar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de personas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población Económicamente Activa PEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incluye a todas las personas de 15 años o más que están trabajando o buscando activamente empleo. Se compone de la población ocupada (quienes tienen un trabajo) y la población desocupada (quienes no tienen trabajo pero lo buscan activamente).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. Encuesta Nacional de Ocupación y Empleo ENOE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población Ocupada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se refiere al total de personas que tienen un empleo, ya sea remunerado o independiente, y que trabajan al menos una hora a la semana.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de ocupación en la entidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de ocupacion en establecimientos de alojamiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producción Pesquera. Valor de la Producción (Peso vivo pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la producción pesquera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONAPESCA. Producción Anual Pesquera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Productividad Laboral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mide la desigualdad económica de una sociedad, mediante la exploración del nivel de concentración que existe en la distribución de los ingresos entre la población.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producto Interno Bruto (millones de pesos) / Porcentaje de ParticipaciÃ³n (VALORES CONSTANTES)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el valor total de los bienes y servicios producidos en una región (en millones de pesos).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millones de pesos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie cosechada (hectáreas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es la superficie de la cual se obtuvo producción, esta variable se genera a partir de que inicia la recolección, la cual puede ser en una sola ocasión como en el caso del Maíz Grano o del Frijol; o en varios cortes como ocurre con los cultivos de recolección, tales como el Tomate Rojo, el Chile verde o la Calabacita, incluye la superficie en que presentó siniestro parcial. Su unidad de medida es la hectarea.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hectáreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Agricultura y Desarrollo Rural SADER. Servicio de Información Agroalimentaria y Pesquera SIAP. Producción Agrícola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie sembrada (hectáreas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es la superficie agrícola en la cual se deposita la semilla de cualquier cultivo, previa preparación del suelo y de la cual se lleva el seguimiento estadístico, es la variable más importante de las que genera la actividad agrícola y cuya unidad de medida es la hectarea.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Condiciones críticas de ocupación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Éste es un indicador de condiciones inadecuadas de empleo desde el punto de vista del tiempo de trabajo, los ingresos o una combinación insatisfactoria de ambos y resulta particularmente sensible en las áreas rurales del país.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Desocupación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el porcentaje de la Población Económicamente Activa (PEA) que está desempleada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Informalidad laboral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proporción de la población ocupada laboralmente vulnerable, ya sea por la naturaleza de la unidad económica para la que trabajan o por carecer de un vínculo laboral no reconocido por su fuente de trabajo de acuerdo con el orden legal vigente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Ocupación en el sector informal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es la proporción de personas que están en la ocupación ocupación informal como porcentaje de la ocupación total. la ocupación ocupación informal comprende a las personas que en su empleo principal o secundario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Ocupación parcial y desocupación/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Considera a la población desocupada y la ocupada que trabajó menos de 15 horas a la semana, no importando si estos ocupados con menos de 15 horas que se añaden se hayan comportado o no como buscadores de empleo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Participación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el porcentaje de la población en edad de trabajar (generalmente de 15 años o más) que está empleada o buscando activamente empleo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Presión general</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incluye además de los desocupados, a los ocupados que buscan empleo, por lo que da una medida global de la competencia por plazas de trabajo conformada no sólo por los que quieren trabajar sino por los que teniendo un empleo quieren cambiarlo o también los que buscan otro más para tener un segundo trabajo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Subocupación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el porcentaje de la población activa que no tiene empleo, pero está buscando activamente uno y está disponible para trabajar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Trabajo asalariado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Representa a la población que percibe de la unidad económica para la que trabaja un sueldo, salario o jornal, por las actividades realizadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trabajadores Asegurados del IMSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puestos de trabajo registrados ante el IMSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total de trabajadores asegurados en el IMSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STPS con datos del IMSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor de la Producción agrícola (miles de pesos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el ingreso total generado por la producción de bienes agrícolas, calculado multiplicando el volumen producido por el precio promedio de los productos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volumen de la Producción Pesquera (Peso vivo kilogramos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volumen de la Producción pesquera en peso vivo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilogramos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volumen de la Producción agrícola (toneladas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es la cantidad de la producción agricola expresada en toneladas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Índice de Competitividad Estatal (lugar nacional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clasifica a los estados mexicanos según su capacidad para atraer y retener inversión y talento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Índice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Mexicano para la Competitividad A.C. IMCO.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gobierno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barometro de Informacion Presupuestal Estatal BIPE (cumplimiento, puntaje obtenido)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mide la calidad de la información presupuestal de las 32 entidades federativas del país.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Mexicano para la Competitividad A.C. IMCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confianza en el Gobierno Estatal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de confianza en el gobierno estatal de la población de 18 años y más</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. Encuesta Nacional de Calidad e Impacto Gubernamental ENCIG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nivel de satisfacción general con los servicios públicos básicos y bajo demanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población de 18 años y más que habita en áreas urbanas de cien mil habitantes y más según satisfacción con los servicios básicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de incidencia de corrupción por cada cien mil habitantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de la población mayor de 18 años, la cual fue víctima de algún acto de corrupción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de prevalencia de la corrupción por cada 100 mil habitantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se calcula dividiendo el número de usuarios(as) que experimentaron algún acto de corrupción en al menos uno de los trámites que realizaron, entre la población que tuvo contacto con algún(a) servidor(a) público(a), multiplicada por cien mil.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Género</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brecha de ingresos por Género #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor absoluto de la diferencia de ingresos mensuales promedio de hombres y mujeres entre los ingresos mensuales promedio de los hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Mexicano para la Competitividad A.C. IMCO. Estados #ConLupaDeGénero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobertura de educación en la primera infancia #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infancias de 0 a 5 años inscritos en una guardería, centro de cuidados o preescolar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delitos sexuales #Con Lupa de Género</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carpetas de investigación de delitos de acoso y hostigamiento sexual por cada 100 mil habitantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dependencia de ingresos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres de 15 años y más que no percibe ingresos monetarios directos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desigualdad en trabajo no remunerado (TNR) #Con Lupa de Género</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas semanales adicionales que dedica una mujer al TNR en comparación con un hombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embarazo Adolescente #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacimientos registrados de madres menores de 20 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emprendedoras formales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emprendedoras en la formalidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homicidios dolosos de mujeres y feminicidios #Con Lupa de Género</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres víctimas de homicidios dolosos y feminicidios por cada 100 mil mujeres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homicidios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Igualdad laboral y no discriminación #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se refiere a iniciativas y herramientas que analizan y miden las condiciones laborales desde una perspectiva de género para identificar y corregir desigualdades específicas que afectan a mujeres y hombres.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inclución financiera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor absoluto de la diferencia entre la media ponderada de los montos otorgados a hombres y mujeres para créditos empresariales y de vivienda entre el promedio de los montos otorgados a hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informalidad #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres ocupadas no agropecuarias en la informalidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jornada laboral larga #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres a menudo enfrentan una "doble jornada", combinando su trabajo remunerado con el trabajo doméstico y de cuidados no remunerado, que suele ser significativamente mayor que el de los hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres Preparadas #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres de 18 años y más con al menos educación media superior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres que quieren trabajar y no pueden #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trabajadoras potenciales desocupadas, subocupadas o disponibles pero no activas en la economía</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oferta de cuidados de adultos mayores #Con Lupa de Género</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidades de cuidados para adultos mayores por cada 100 mil habitantes de 65 años y más</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percepción de inseguridad en transporte público #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres que dejaron de usar transporte público por temor a ser víctima de algún delito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permisos de paternidad #Con Lupa de Género</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permiso de paternidad remunerado para los trabajadores del gobierno del Estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permiso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pobreza laboral #Con Lupa de Género (Porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres con ingreso laboral inferior al costo de la canasta alimentaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propiedad de la vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres con propiedad o copropiedad legal de vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medio ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Areas naturales protegidas superficie terrestre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie terrestre considerada como área natural protegidas superficie terrestre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Medio Ambiente y Recursos Naturales. Dirección General de Estadística e Información Ambiental. CONANP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacidad instalada en las PTARs (Litros por segundo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacidad Instalada de las Plantas tratadoras de aguas residuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Litros por segundo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. México en Cifras. Tabulados de Integración. Medio Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plantas Tratadoras de Aguas residuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de plantas tratadoras de aguas residuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de plantas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volumen tratado en las PTARs (Millones m3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volumen de agua residual tratada en la Planta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millones de metros cúbicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seguridad Pública</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cifra negra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se refiere a la cantidad de delitos que no se registran en las estadísticas oficiales, porque no son denunciados por la víctima, no se inicia una carpeta de investigación, o no son descubiertos por las autoridades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. Encuesta Nacional de Victimización y Percepción sobre Seguridad Pública (ENVIPE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delitos denunciados (porcentaje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de delitos que son denunciados ante el Ministerio público e inicia una carpeta de investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extorsión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de extorsión registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública SESNSP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Femicicidios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de femicicidios registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de homicidios (doloso y culposo) registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incidencia delictiva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total de delitos registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indice de Paz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panorama del nivel de paz en las entidades federativa de México</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Institute Economics &amp; Peace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lesiones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de lesiones registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortalidad Defunciones registradas en Accidentes de Tránsito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de muertes causadas por accidente de tránsito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de muertos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narcomenudeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de homicidios registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de Accidentes de tránsito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Información sobre el número de accidentes de tránsito terrestre registrados por los gobiernos municipales, así como el total de víctimas muertas en el lugar del accidente y heridas con lesiones leves y/o graves.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de accidentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percepcion sobre Seguridad Publica Inseguro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percepción de la población de 18 años y más respecto de la situación que guarda la seguridad pública (seguro) en su entidad federativa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percepcion sobre Seguridad Publica Seguro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percepción de la población de 18 años y más respecto de la situación que guarda la seguridad pública (inseguro) en su entidad federativa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percepción sobre tema de Inseguridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percepción de la población de 18 años y más respecto de la situación que guarda la inseguridad pública en su entidad federativa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robo a Casa Habitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de robo a casa habitación registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robo a Negocio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de robo a negocios registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robo de Vehículos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos derobo de vehiculos automotores registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secuestro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de secuestro registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa bruta de homicidios por cada 100 mil habitantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el número de defunciones registradas como presuntos homicidios en los certificados de defunción durante el año, entre el total de la población a mitad del año de referencia, multiplicado por 100,000.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Incidencia Delictiva (100 mil hab)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el número de delitos registradas entre el total de la población a mitad del año de referencia, multiplicado por 100,000.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Prevalencia Delictiva (100 mil hab) personas, hogares o propiedades que han sido víctimas de un delito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mide el número de víctimas de delitos por cada 100,000 habitantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de violación (simple y equiparada) registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violencia familiar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casos de violencia familira registrados a traves de Carpetas de Investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abandono escolar Educación Superior (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el total de alumnos que abandonan las actividades escolares antes de concluir algún grado o nivel educativo, expresado como porcentaje del total de alumnos inscritos en el ciclo escolar. El resultado se multiplica por cien.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEP. Estadística Educativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobertura Educación Primaria (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indica el porcentaje de alumnos atendidos en un nivel educativo, con respecto a la población que representa la edad para cursar dicho nivel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobertura educacíón Presescolar (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobertura educacíón Secundaria (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobertura educacíónMedia Superior (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indica el porcentaje de alumnos atendidos en un nivel educativo, con  respecto a la población que representa la edad para cursar dicho nivel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defunciones Registradas EDR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defunciones registradas que permitan caracterizar el fenómeno de la mortalidad en el país.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defunciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. Estadísticas de Defunciones Registradas (EDR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eficiencia terminal Primaria (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es el porcentaje de alumnos que concluyen un nivel educativo, respecto al número de alumnos que ingresaron a este nivel en la cohorte correspondiente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eficiencia terminal educación Secundaria (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grado promedio de escolaridad (años)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de años que, en promedio, aprobaron las personas de 15 años y más, en el Sistema Educativo Nacional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinquenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población con Carencia por acceso a la alimentación nutritiva y de calidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra con carencia al acceso a la alimentación nutritiva y de calidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población con Carencia por acceso a la seguridad social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra con carencia a la seguridad social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población con Carencia por acceso a los servicios básicos en la vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra con carencia a los accesos de servicios básicos en la vievienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población con Carencia por acceso a los servicios de salud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra con carencia a los servicios de salud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población con Carencia por calidad y espacios de la vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra con carencia por calidad y espacios de la vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población con Población con Ingreso Inferior a la Línea de pobreza extrema por ingresos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población con Ingreso Inferior a la Línea de pobreza extrema por ingresos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población con Población con Ingreso Inferior a la Línea de pobreza por ingresos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población con Ingreso Inferior a la Línea de pobreza por ingresos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población con Rezago Educativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentracon rezago educativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población en situación de Pobreza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra en situación de pobreza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Población en situación de Pobreza Moderada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra en situación de pobreza moderada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la Poblaciónn en situación de Pobreza Extrema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra en situación de pobreza extrema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la población vulnerable por ingresos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Población que se encuentra en situación de vulnerabilidad por ingresos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Abandono Escolar Media Superior (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de Abandono escolar Educación Primaria (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de ocupación infantil no permitida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La ocupación infantil no permitida incluye trabajos que por ley no deben realizar menores de 18 años, ya que ponen en riesgo su salud, seguridad o desarrollo integral.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trianual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INEGI. Encuesta Nacional de Trabajo Infantil (ENTI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa de quehaceres domésticos en condiciones no adecuadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son actividades no remuneradas dentro del hogar que afectan la salud o integridad de quienes las realizan, ya sea por ser peligrosas o por extenderse a horarios prolongados</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="379">
+  <si>
+    <t>Tema</t>
+  </si>
+  <si>
+    <t>Indicador</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Unidad de medida</t>
+  </si>
+  <si>
+    <t>En razón de algo</t>
+  </si>
+  <si>
+    <t>Sentido</t>
+  </si>
+  <si>
+    <t>temporalidad</t>
+  </si>
+  <si>
+    <t>Fuente</t>
+  </si>
+  <si>
+    <t>Económico</t>
+  </si>
+  <si>
+    <t>Aves. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la Producción de aves.</t>
+  </si>
+  <si>
+    <t>Miles de pesos</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Más es mejor</t>
+  </si>
+  <si>
+    <t>Anual</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural SADER. Servicio de Información Agroalimentaria y Pesquera SIAP. Producción Ganadera</t>
+  </si>
+  <si>
+    <t>Aves. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de aves.</t>
+  </si>
+  <si>
+    <t>Toneladas</t>
+  </si>
+  <si>
+    <t>Cera. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la producción de cera.</t>
+  </si>
+  <si>
+    <t>Cera. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de cera.</t>
+  </si>
+  <si>
+    <t>Crecimiento Economico</t>
+  </si>
+  <si>
+    <t>Se refiere al incremento en la producción de bienes y servicios en una economía de un periodo a otro.</t>
+  </si>
+  <si>
+    <t>Talvez porcentaje</t>
+  </si>
+  <si>
+    <t>Trimestral</t>
+  </si>
+  <si>
+    <t>México ¿Cómo vamos?</t>
+  </si>
+  <si>
+    <t>Cuartos de Hospedaje según categoría (1 estrella)</t>
+  </si>
+  <si>
+    <t>Número de cuartos</t>
+  </si>
+  <si>
+    <t>INEGI. México en Cifras. Tabulados de Integración. Turismo</t>
+  </si>
+  <si>
+    <t>Cuartos de Hospedaje según categoría (2 estrellas)</t>
+  </si>
+  <si>
+    <t>Cuartos de Hospedaje según categoría (3 estrellas)</t>
+  </si>
+  <si>
+    <t>Cuartos de Hospedaje según categoría (4 estrellas)</t>
+  </si>
+  <si>
+    <t>Cuartos de Hospedaje según categoría (5 estrellas)</t>
+  </si>
+  <si>
+    <t>Cuartos de Hospedaje según categoría (sin categoría)</t>
+  </si>
+  <si>
+    <t>Cuartos de establecimientos de Hospedaje</t>
+  </si>
+  <si>
+    <t>Valor absoluto</t>
+  </si>
+  <si>
+    <t>Desigualdad Laboral</t>
+  </si>
+  <si>
+    <t>La desigualdad laboral se manifiesta en la brecha de género, la informalidad y la brecha salarial</t>
+  </si>
+  <si>
+    <t>Talvez coeficiente de Gini entre 0 y 1</t>
+  </si>
+  <si>
+    <t>Menos es mejor</t>
+  </si>
+  <si>
+    <t>Deuda Pública (Porcentaje del PIB)</t>
+  </si>
+  <si>
+    <t>Compara la variación anual de la deuda neta del sector público federal con la variación anual del PIB a precios corrientes</t>
+  </si>
+  <si>
+    <t>Porcentaje</t>
+  </si>
+  <si>
+    <t>Empleos formales generados</t>
+  </si>
+  <si>
+    <t>Refleja el número de puestos de trabajo formales creados o eliminados en el registro del IMSS.</t>
+  </si>
+  <si>
+    <t>Número de puestos de trabajo</t>
+  </si>
+  <si>
+    <t>Mensual</t>
+  </si>
+  <si>
+    <t>Establecimiento de Hospedaje</t>
+  </si>
+  <si>
+    <t>Establecimiento de Hospedaje según categoría (1 estrella)</t>
+  </si>
+  <si>
+    <t>Número de establecimientos</t>
+  </si>
+  <si>
+    <t>Establecimiento de Hospedaje según categoría (2 estrellas)</t>
+  </si>
+  <si>
+    <t>Establecimiento de Hospedaje según categoría (3 estrellas)</t>
+  </si>
+  <si>
+    <t>Establecimiento de Hospedaje según categoría (4 estrellas)</t>
+  </si>
+  <si>
+    <t>Establecimiento de Hospedaje según categoría (5 estrellas)</t>
+  </si>
+  <si>
+    <t>Establecimientos de Hospedaje según categoría (sin categoría)</t>
+  </si>
+  <si>
+    <t>Exportaciones por Entidad Federativa</t>
+  </si>
+  <si>
+    <t>Información referente al valor de las exportaciones de mercancías por entidad federativa, que permite conocer la participación de cada una de ellas en el intercambio comercial que realiza México con el resto del mundo.</t>
+  </si>
+  <si>
+    <t>Millones de dólares</t>
+  </si>
+  <si>
+    <t>INEGI</t>
+  </si>
+  <si>
+    <t>Ganado Bovino. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la Producción de ganado bovino en pie.</t>
+  </si>
+  <si>
+    <t>Ganado Bovino. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de ganado bovino en pie.</t>
+  </si>
+  <si>
+    <t>Ganado Caprino. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la Producción de ganado caprino en pie.</t>
+  </si>
+  <si>
+    <t>Ganado Caprino. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de ganado caprino en pie.</t>
+  </si>
+  <si>
+    <t>Ganado Ovino. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la Producción de ganado ovino en pie.</t>
+  </si>
+  <si>
+    <t>Ganado Ovino. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de ganado ovino en pie.</t>
+  </si>
+  <si>
+    <t>Ganado Porcino. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la Producción de ganado porcino en pie.</t>
+  </si>
+  <si>
+    <t>Ganado Porcino. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de ganado porcino en pie.</t>
+  </si>
+  <si>
+    <t>Gasto corriente promedio trimestral por hogar</t>
+  </si>
+  <si>
+    <t>Gasto corriente promedio trimestral en los hogares</t>
+  </si>
+  <si>
+    <t>Pesos</t>
+  </si>
+  <si>
+    <t>Bianual</t>
+  </si>
+  <si>
+    <t>INEGI. Encuesta Nacional de Ingreso Gasto en los Hogares ENIGH</t>
+  </si>
+  <si>
+    <t>Guajolotes. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la Producción de guajolotes.</t>
+  </si>
+  <si>
+    <t>Guajolotes. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de guajolotes.</t>
+  </si>
+  <si>
+    <t>Huevo para Plato. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la producción de huevo para plato.</t>
+  </si>
+  <si>
+    <t>Huevo para plato. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de huevo para plato.</t>
+  </si>
+  <si>
+    <t>Indicador Mensual de la Actividad Industrial por Entidad Federativa IMAIEF</t>
+  </si>
+  <si>
+    <t>Proporciona información estadística de corto plazo en el ámbito estatal que permite dar seguimiento al comportamiento de las actividades secundarias en los estados.</t>
+  </si>
+  <si>
+    <t>Indice</t>
+  </si>
+  <si>
+    <t>Indicador Trimestral de la Actividad Economica Estatal ITAEE</t>
+  </si>
+  <si>
+    <t>Ofrece un panorama sobre la evolución económica de las entidades federativas del país.</t>
+  </si>
+  <si>
+    <t>Informalidad Laboral</t>
+  </si>
+  <si>
+    <t>Proporción de la población ocupada que son laboralmente vulnerables por la naturaleza de la unidad económica para la que trabajan, así como aquellas personas ocupadas cuyo vínculo laboral no es reconocido por su fuente de trabajo.</t>
+  </si>
+  <si>
+    <t>Casos por cada 100 mil habitantes</t>
+  </si>
+  <si>
+    <t>Ingreso corriente promedio trimestral por hogar</t>
+  </si>
+  <si>
+    <t>Se compone del ingreso corriente total y de las percepciones financieras y de capital.</t>
+  </si>
+  <si>
+    <t>INEGI. Encuesta Nacional de Ingresos y Gastos de los Hogares (ENIGH).</t>
+  </si>
+  <si>
+    <t>Ingresos por Remesas</t>
+  </si>
+  <si>
+    <t>Los ingresos por remesas son el dinero que envían los trabajadores migrantes a sus familias en sus países de origen.</t>
+  </si>
+  <si>
+    <t>Banco de México</t>
+  </si>
+  <si>
+    <t>Inversion Extranjera Directa IED</t>
+  </si>
+  <si>
+    <t>Es la suma de los capitales a largo plazo que provienen de otros países y entran a México para la creación de empresas agrícolas, industriales y de servicios. El término clave es “largo plazo”, ya que esto es lo que la separa de cualquier otro flujo de capital extranjero.</t>
+  </si>
+  <si>
+    <t>Secretaría de Economía</t>
+  </si>
+  <si>
+    <t>Lana. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la producción de lana.</t>
+  </si>
+  <si>
+    <t>Lana. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de lana.</t>
+  </si>
+  <si>
+    <t>Leche de Bovino. Valor de la Producción miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la producción de leche de bovino.</t>
+  </si>
+  <si>
+    <t>Leche de Bovino. Volumen de la Producción (miles de litros)</t>
+  </si>
+  <si>
+    <t>Producción de leche de bovino.</t>
+  </si>
+  <si>
+    <t>Miles de litros</t>
+  </si>
+  <si>
+    <t>Leche de Caprino. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la producción de leche de ganado caprino.</t>
+  </si>
+  <si>
+    <t>Leche de Caprino. Volumen de la Producción (miles de litros)</t>
+  </si>
+  <si>
+    <t>Producción de leche de ganado caprino.</t>
+  </si>
+  <si>
+    <t>Llegada de Turistas Totales a la Entidad</t>
+  </si>
+  <si>
+    <t>Llegada de Turistas a la Entidad por Tipo de Turismo (extranjeros)</t>
+  </si>
+  <si>
+    <t>Llegada de Turistas a la Entidad por Tipo de Turismo (nacionales)</t>
+  </si>
+  <si>
+    <t>Longitud de la Red Carretera Federal (kilometros)</t>
+  </si>
+  <si>
+    <t>Registra el total de kilómetros de la red carretera federal.</t>
+  </si>
+  <si>
+    <t>Kilometros</t>
+  </si>
+  <si>
+    <t>INEGI. México en Cifras. Tabulados de Integración. Transporte</t>
+  </si>
+  <si>
+    <t>Longitud de la Red de Alimentadoras estatales (kilometros</t>
+  </si>
+  <si>
+    <t>Registra el total de kilómetros de la red de carreteras alimentadoras estatales.</t>
+  </si>
+  <si>
+    <t>Longitud de la Red de Brechas Mejoradas (kilometros)</t>
+  </si>
+  <si>
+    <t>Registra el total de kilómetros de brechas mejoradas.</t>
+  </si>
+  <si>
+    <t>Longitud de la Red de Caminos Rurales (kilometros)</t>
+  </si>
+  <si>
+    <t>Registra el total de kilómetros de la red de caminos rurales.</t>
+  </si>
+  <si>
+    <t>Miel. Valor de la Producción (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la producción de miel.</t>
+  </si>
+  <si>
+    <t>Miel. Volumen de la Producción (toneladas)</t>
+  </si>
+  <si>
+    <t>Producción de miel.</t>
+  </si>
+  <si>
+    <t>Oferta de alojamiento en la entidad (cuartos)</t>
+  </si>
+  <si>
+    <t>Disponibilidad de cuartos en los establecimientos de alojamiento</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo. DataTur</t>
+  </si>
+  <si>
+    <t>Patentes</t>
+  </si>
+  <si>
+    <t>Una patente es un derecho exclusivo que concede el Estado para la protección de una invención, la que proporciona derechos exclusivos que permitirán utilizar y explotar su invención e impedir que terceros la utilicen sin su consentimiento.</t>
+  </si>
+  <si>
+    <t>Número de patentes registradas</t>
+  </si>
+  <si>
+    <t>Instituto Mexicano de la Pro´piedad Industrial</t>
+  </si>
+  <si>
+    <t>Población Desocupada</t>
+  </si>
+  <si>
+    <t>Se refiere a personas que no tienen un trabajo pero están activamente buscando uno y están disponibles para trabajar.</t>
+  </si>
+  <si>
+    <t>Número de personas</t>
+  </si>
+  <si>
+    <t>Población Económicamente Activa PEA</t>
+  </si>
+  <si>
+    <t>Incluye a todas las personas de 15 años o más que están trabajando o buscando activamente empleo. Se compone de la población ocupada (quienes tienen un trabajo) y la población desocupada (quienes no tienen trabajo pero lo buscan activamente).</t>
+  </si>
+  <si>
+    <t>INEGI. Encuesta Nacional de Ocupación y Empleo ENOE</t>
+  </si>
+  <si>
+    <t>Población Ocupada</t>
+  </si>
+  <si>
+    <t>Se refiere al total de personas que tienen un empleo, ya sea remunerado o independiente, y que trabajan al menos una hora a la semana.</t>
+  </si>
+  <si>
+    <t>Porcentaje de ocupación en la entidad</t>
+  </si>
+  <si>
+    <t>Porcentaje de ocupacion en establecimientos de alojamiento</t>
+  </si>
+  <si>
+    <t>Producción Pesquera. Valor de la Producción (Peso vivo pesos)</t>
+  </si>
+  <si>
+    <t>Valor de la producción pesquera.</t>
+  </si>
+  <si>
+    <t>CONAPESCA. Producción Anual Pesquera</t>
+  </si>
+  <si>
+    <t>Productividad Laboral</t>
+  </si>
+  <si>
+    <t>Mide la desigualdad económica de una sociedad, mediante la exploración del nivel de concentración que existe en la distribución de los ingresos entre la población.</t>
+  </si>
+  <si>
+    <t>Producto Interno Bruto (millones de pesos) / Porcentaje de ParticipaciÃ³n (VALORES CONSTANTES)</t>
+  </si>
+  <si>
+    <t>Es el valor total de los bienes y servicios producidos en una región (en millones de pesos).</t>
+  </si>
+  <si>
+    <t>Millones de pesos</t>
+  </si>
+  <si>
+    <t>Superficie cosechada (hectáreas)</t>
+  </si>
+  <si>
+    <t>Es la superficie de la cual se obtuvo producción, esta variable se genera a partir de que inicia la recolección, la cual puede ser en una sola ocasión como en el caso del Maíz Grano o del Frijol; o en varios cortes como ocurre con los cultivos de recolección, tales como el Tomate Rojo, el Chile verde o la Calabacita, incluye la superficie en que presentó siniestro parcial. Su unidad de medida es la hectarea.</t>
+  </si>
+  <si>
+    <t>Hectáreas</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural SADER. Servicio de Información Agroalimentaria y Pesquera SIAP. Producción Agrícola</t>
+  </si>
+  <si>
+    <t>Superficie sembrada (hectáreas)</t>
+  </si>
+  <si>
+    <t>Es la superficie agrícola en la cual se deposita la semilla de cualquier cultivo, previa preparación del suelo y de la cual se lleva el seguimiento estadístico, es la variable más importante de las que genera la actividad agrícola y cuya unidad de medida es la hectarea.</t>
+  </si>
+  <si>
+    <t>Tasa de Condiciones críticas de ocupación</t>
+  </si>
+  <si>
+    <t>Éste es un indicador de condiciones inadecuadas de empleo desde el punto de vista del tiempo de trabajo, los ingresos o una combinación insatisfactoria de ambos y resulta particularmente sensible en las áreas rurales del país.</t>
+  </si>
+  <si>
+    <t>Tasa de Desocupación</t>
+  </si>
+  <si>
+    <t>Es el porcentaje de la Población Económicamente Activa (PEA) que está desempleada.</t>
+  </si>
+  <si>
+    <t>Tasa de Informalidad laboral</t>
+  </si>
+  <si>
+    <t>Proporción de la población ocupada laboralmente vulnerable, ya sea por la naturaleza de la unidad económica para la que trabajan o por carecer de un vínculo laboral no reconocido por su fuente de trabajo de acuerdo con el orden legal vigente.</t>
+  </si>
+  <si>
+    <t>Tasa de Ocupación en el sector informal</t>
+  </si>
+  <si>
+    <t>Es la proporción de personas que están en la ocupación ocupación informal como porcentaje de la ocupación total. la ocupación ocupación informal comprende a las personas que en su empleo principal o secundario</t>
+  </si>
+  <si>
+    <t>Tasa de Ocupación parcial y desocupación/</t>
+  </si>
+  <si>
+    <t>Considera a la población desocupada y la ocupada que trabajó menos de 15 horas a la semana, no importando si estos ocupados con menos de 15 horas que se añaden se hayan comportado o no como buscadores de empleo.</t>
+  </si>
+  <si>
+    <t>Tasa de Participación</t>
+  </si>
+  <si>
+    <t>Es el porcentaje de la población en edad de trabajar (generalmente de 15 años o más) que está empleada o buscando activamente empleo.</t>
+  </si>
+  <si>
+    <t>Tasa de Presión general</t>
+  </si>
+  <si>
+    <t>Incluye además de los desocupados, a los ocupados que buscan empleo, por lo que da una medida global de la competencia por plazas de trabajo conformada no sólo por los que quieren trabajar sino por los que teniendo un empleo quieren cambiarlo o también los que buscan otro más para tener un segundo trabajo.</t>
+  </si>
+  <si>
+    <t>Tasa de Subocupación</t>
+  </si>
+  <si>
+    <t>Es el porcentaje de la población activa que no tiene empleo, pero está buscando activamente uno y está disponible para trabajar.</t>
+  </si>
+  <si>
+    <t>Tasa de Trabajo asalariado</t>
+  </si>
+  <si>
+    <t>Representa a la población que percibe de la unidad económica para la que trabaja un sueldo, salario o jornal, por las actividades realizadas</t>
+  </si>
+  <si>
+    <t>Trabajadores Asegurados del IMSS</t>
+  </si>
+  <si>
+    <t>Puestos de trabajo registrados ante el IMSS</t>
+  </si>
+  <si>
+    <t>Total de trabajadores asegurados en el IMSS</t>
+  </si>
+  <si>
+    <t>STPS con datos del IMSS</t>
+  </si>
+  <si>
+    <t>Valor de la Producción agrícola (miles de pesos)</t>
+  </si>
+  <si>
+    <t>Es el ingreso total generado por la producción de bienes agrícolas, calculado multiplicando el volumen producido por el precio promedio de los productos</t>
+  </si>
+  <si>
+    <t>Volumen de la Producción Pesquera (Peso vivo kilogramos)</t>
+  </si>
+  <si>
+    <t>Volumen de la Producción pesquera en peso vivo.</t>
+  </si>
+  <si>
+    <t>Kilogramos</t>
+  </si>
+  <si>
+    <t>Volumen de la Producción agrícola (toneladas)</t>
+  </si>
+  <si>
+    <t>Es la cantidad de la producción agricola expresada en toneladas</t>
+  </si>
+  <si>
+    <t>Índice de Competitividad Estatal (lugar nacional)</t>
+  </si>
+  <si>
+    <t>Clasifica a los estados mexicanos según su capacidad para atraer y retener inversión y talento</t>
+  </si>
+  <si>
+    <t>Índice</t>
+  </si>
+  <si>
+    <t>Instituto Mexicano para la Competitividad A.C. IMCO.</t>
+  </si>
+  <si>
+    <t>Gobierno</t>
+  </si>
+  <si>
+    <t>Barometro de Informacion Presupuestal Estatal BIPE (cumplimiento, puntaje obtenido)</t>
+  </si>
+  <si>
+    <t>Mide la calidad de la información presupuestal de las 32 entidades federativas del país.</t>
+  </si>
+  <si>
+    <t>Instituto Mexicano para la Competitividad A.C. IMCO</t>
+  </si>
+  <si>
+    <t>Confianza en el Gobierno Estatal</t>
+  </si>
+  <si>
+    <t>Porcentaje de confianza en el gobierno estatal de la población de 18 años y más</t>
+  </si>
+  <si>
+    <t>INEGI. Encuesta Nacional de Calidad e Impacto Gubernamental ENCIG</t>
+  </si>
+  <si>
+    <t>Nivel de satisfacción general con los servicios públicos básicos y bajo demanda</t>
+  </si>
+  <si>
+    <t>Población de 18 años y más que habita en áreas urbanas de cien mil habitantes y más según satisfacción con los servicios básicos</t>
+  </si>
+  <si>
+    <t>Tasa de incidencia de corrupción por cada cien mil habitantes</t>
+  </si>
+  <si>
+    <t>Tasa de la población mayor de 18 años, la cual fue víctima de algún acto de corrupción</t>
+  </si>
+  <si>
+    <t>Tasa de prevalencia de la corrupción por cada 100 mil habitantes</t>
+  </si>
+  <si>
+    <t>Se calcula dividiendo el número de usuarios(as) que experimentaron algún acto de corrupción en al menos uno de los trámites que realizaron, entre la población que tuvo contacto con algún(a) servidor(a) público(a), multiplicada por cien mil.</t>
+  </si>
+  <si>
+    <t>Género</t>
+  </si>
+  <si>
+    <t>Brecha de ingresos por Género #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Valor absoluto de la diferencia de ingresos mensuales promedio de hombres y mujeres entre los ingresos mensuales promedio de los hombres</t>
+  </si>
+  <si>
+    <t>Instituto Mexicano para la Competitividad A.C. IMCO. Estados #ConLupaDeGénero</t>
+  </si>
+  <si>
+    <t>Cobertura de educación en la primera infancia #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Infancias de 0 a 5 años inscritos en una guardería, centro de cuidados o preescolar</t>
+  </si>
+  <si>
+    <t>Delitos sexuales #Con Lupa de Género</t>
+  </si>
+  <si>
+    <t>Carpetas de investigación de delitos de acoso y hostigamiento sexual por cada 100 mil habitantes</t>
+  </si>
+  <si>
+    <t>Delito</t>
+  </si>
+  <si>
+    <t>Dependencia de ingresos</t>
+  </si>
+  <si>
+    <t>Mujeres de 15 años y más que no percibe ingresos monetarios directos</t>
+  </si>
+  <si>
+    <t>Desigualdad en trabajo no remunerado (TNR) #Con Lupa de Género</t>
+  </si>
+  <si>
+    <t>Horas semanales adicionales que dedica una mujer al TNR en comparación con un hombre</t>
+  </si>
+  <si>
+    <t>Tiempo</t>
+  </si>
+  <si>
+    <t>Embarazo Adolescente #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Nacimientos registrados de madres menores de 20 años</t>
+  </si>
+  <si>
+    <t>Emprendedoras formales</t>
+  </si>
+  <si>
+    <t>Emprendedoras en la formalidad</t>
+  </si>
+  <si>
+    <t>Homicidios dolosos de mujeres y feminicidios #Con Lupa de Género</t>
+  </si>
+  <si>
+    <t>Mujeres víctimas de homicidios dolosos y feminicidios por cada 100 mil mujeres</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Igualdad laboral y no discriminación #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>se refiere a iniciativas y herramientas que analizan y miden las condiciones laborales desde una perspectiva de género para identificar y corregir desigualdades específicas que afectan a mujeres y hombres.</t>
+  </si>
+  <si>
+    <t>Inclución financiera</t>
+  </si>
+  <si>
+    <t>Valor absoluto de la diferencia entre la media ponderada de los montos otorgados a hombres y mujeres para créditos empresariales y de vivienda entre el promedio de los montos otorgados a hombres</t>
+  </si>
+  <si>
+    <t>Informalidad #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Mujeres ocupadas no agropecuarias en la informalidad</t>
+  </si>
+  <si>
+    <t>Jornada laboral larga #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Mujeres a menudo enfrentan una "doble jornada", combinando su trabajo remunerado con el trabajo doméstico y de cuidados no remunerado, que suele ser significativamente mayor que el de los hombres</t>
+  </si>
+  <si>
+    <t>Mujeres Preparadas #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Mujeres de 18 años y más con al menos educación media superior</t>
+  </si>
+  <si>
+    <t>Mujeres que quieren trabajar y no pueden #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Trabajadoras potenciales desocupadas, subocupadas o disponibles pero no activas en la economía</t>
+  </si>
+  <si>
+    <t>Oferta de cuidados de adultos mayores #Con Lupa de Género</t>
+  </si>
+  <si>
+    <t>Unidades de cuidados para adultos mayores por cada 100 mil habitantes de 65 años y más</t>
+  </si>
+  <si>
+    <t>Tasa</t>
+  </si>
+  <si>
+    <t>Percepción de inseguridad en transporte público #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Mujeres que dejaron de usar transporte público por temor a ser víctima de algún delito</t>
+  </si>
+  <si>
+    <t>Permisos de paternidad #Con Lupa de Género</t>
+  </si>
+  <si>
+    <t>Permiso de paternidad remunerado para los trabajadores del gobierno del Estado</t>
+  </si>
+  <si>
+    <t>Permiso</t>
+  </si>
+  <si>
+    <t>Pobreza laboral #Con Lupa de Género (Porcentaje)</t>
+  </si>
+  <si>
+    <t>Mujeres con ingreso laboral inferior al costo de la canasta alimentaria</t>
+  </si>
+  <si>
+    <t>Propiedad de la vivienda</t>
+  </si>
+  <si>
+    <t>Mujeres con propiedad o copropiedad legal de vivienda</t>
+  </si>
+  <si>
+    <t>Medio ambiente</t>
+  </si>
+  <si>
+    <t>Areas naturales protegidas superficie terrestre</t>
+  </si>
+  <si>
+    <t>Superficie terrestre considerada como área natural protegidas superficie terrestre</t>
+  </si>
+  <si>
+    <t>Secretaría de Medio Ambiente y Recursos Naturales. Dirección General de Estadística e Información Ambiental. CONANP.</t>
+  </si>
+  <si>
+    <t>Capacidad instalada en las PTARs (Litros por segundo)</t>
+  </si>
+  <si>
+    <t>Capacidad Instalada de las Plantas tratadoras de aguas residuales</t>
+  </si>
+  <si>
+    <t>Litros por segundo</t>
+  </si>
+  <si>
+    <t>INEGI. México en Cifras. Tabulados de Integración. Medio Ambiente</t>
+  </si>
+  <si>
+    <t>Plantas Tratadoras de Aguas residuales</t>
+  </si>
+  <si>
+    <t>Número de plantas tratadoras de aguas residuales</t>
+  </si>
+  <si>
+    <t>Número de plantas</t>
+  </si>
+  <si>
+    <t>Volumen tratado en las PTARs (Millones m3)</t>
+  </si>
+  <si>
+    <t>Volumen de agua residual tratada en la Planta</t>
+  </si>
+  <si>
+    <t>Millones de metros cúbicos</t>
+  </si>
+  <si>
+    <t>Seguridad Pública</t>
+  </si>
+  <si>
+    <t>Cifra negra</t>
+  </si>
+  <si>
+    <t>Se refiere a la cantidad de delitos que no se registran en las estadísticas oficiales, porque no son denunciados por la víctima, no se inicia una carpeta de investigación, o no son descubiertos por las autoridades</t>
+  </si>
+  <si>
+    <t>INEGI. Encuesta Nacional de Victimización y Percepción sobre Seguridad Pública (ENVIPE)</t>
+  </si>
+  <si>
+    <t>Delitos denunciados (porcentaje)</t>
+  </si>
+  <si>
+    <t>Porcentaje de delitos que son denunciados ante el Ministerio público e inicia una carpeta de investigación</t>
+  </si>
+  <si>
+    <t>Extorsión</t>
+  </si>
+  <si>
+    <t>Casos de extorsión registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública SESNSP</t>
+  </si>
+  <si>
+    <t>Femicicidios</t>
+  </si>
+  <si>
+    <t>Casos de femicicidios registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Casos de homicidios (doloso y culposo) registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Incidencia delictiva</t>
+  </si>
+  <si>
+    <t>Total de delitos registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Indice de Paz</t>
+  </si>
+  <si>
+    <t>Panorama del nivel de paz en las entidades federativa de México</t>
+  </si>
+  <si>
+    <t>Institute Economics &amp; Peace</t>
+  </si>
+  <si>
+    <t>Lesiones</t>
+  </si>
+  <si>
+    <t>Casos de lesiones registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Mortalidad Defunciones registradas en Accidentes de Tránsito</t>
+  </si>
+  <si>
+    <t>Número de muertes causadas por accidente de tránsito</t>
+  </si>
+  <si>
+    <t>Número de muertos</t>
+  </si>
+  <si>
+    <t>Narcomenudeo</t>
+  </si>
+  <si>
+    <t>Casos de homicidios registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Número de Accidentes de tránsito</t>
+  </si>
+  <si>
+    <t>Información sobre el número de accidentes de tránsito terrestre registrados por los gobiernos municipales, así como el total de víctimas muertas en el lugar del accidente y heridas con lesiones leves y/o graves.</t>
+  </si>
+  <si>
+    <t>Número de accidentes</t>
+  </si>
+  <si>
+    <t>Percepcion sobre Seguridad Publica Inseguro</t>
+  </si>
+  <si>
+    <t>Percepción de la población de 18 años y más respecto de la situación que guarda la seguridad pública (seguro) en su entidad federativa.</t>
+  </si>
+  <si>
+    <t>Percepcion sobre Seguridad Publica Seguro</t>
+  </si>
+  <si>
+    <t>Percepción de la población de 18 años y más respecto de la situación que guarda la seguridad pública (inseguro) en su entidad federativa.</t>
+  </si>
+  <si>
+    <t>Percepción sobre tema de Inseguridad</t>
+  </si>
+  <si>
+    <t>Percepción de la población de 18 años y más respecto de la situación que guarda la inseguridad pública en su entidad federativa.</t>
+  </si>
+  <si>
+    <t>Robo a Casa Habitación</t>
+  </si>
+  <si>
+    <t>Casos de robo a casa habitación registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Robo a Negocio</t>
+  </si>
+  <si>
+    <t>Casos de robo a negocios registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Robo de Vehículos</t>
+  </si>
+  <si>
+    <t>Casos derobo de vehiculos automotores registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Secuestro</t>
+  </si>
+  <si>
+    <t>Casos de secuestro registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Tasa bruta de homicidios por cada 100 mil habitantes</t>
+  </si>
+  <si>
+    <t>Es el número de defunciones registradas como presuntos homicidios en los certificados de defunción durante el año, entre el total de la población a mitad del año de referencia, multiplicado por 100,000.</t>
+  </si>
+  <si>
+    <t>Tasa de Incidencia Delictiva (100 mil hab)</t>
+  </si>
+  <si>
+    <t>Es el número de delitos registradas entre el total de la población a mitad del año de referencia, multiplicado por 100,000.</t>
+  </si>
+  <si>
+    <t>Tasa de Prevalencia Delictiva (100 mil hab) personas, hogares o propiedades que han sido víctimas de un delito</t>
+  </si>
+  <si>
+    <t>Mide el número de víctimas de delitos por cada 100,000 habitantes</t>
+  </si>
+  <si>
+    <t>Violacion</t>
+  </si>
+  <si>
+    <t>Casos de violación (simple y equiparada) registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Violencia familiar</t>
+  </si>
+  <si>
+    <t>Casos de violencia familira registrados a traves de Carpetas de Investigación</t>
+  </si>
+  <si>
+    <t>Social</t>
+  </si>
+  <si>
+    <t>Abandono escolar Educación Superior (%)</t>
+  </si>
+  <si>
+    <t>Es el total de alumnos que abandonan las actividades escolares antes de concluir algún grado o nivel educativo, expresado como porcentaje del total de alumnos inscritos en el ciclo escolar. El resultado se multiplica por cien.</t>
+  </si>
+  <si>
+    <t>SEP. Estadística Educativa</t>
+  </si>
+  <si>
+    <t>Cobertura Educación Primaria (%)</t>
+  </si>
+  <si>
+    <t>Indica el porcentaje de alumnos atendidos en un nivel educativo, con respecto a la población que representa la edad para cursar dicho nivel.</t>
+  </si>
+  <si>
+    <t>Cobertura educacíón Presescolar (%)</t>
+  </si>
+  <si>
+    <t>Cobertura educacíón Secundaria (%)</t>
+  </si>
+  <si>
+    <t>Cobertura educacíónMedia Superior (%)</t>
+  </si>
+  <si>
+    <t>Indica el porcentaje de alumnos atendidos en un nivel educativo, con  respecto a la población que representa la edad para cursar dicho nivel.</t>
+  </si>
+  <si>
+    <t>Defunciones Registradas EDR</t>
+  </si>
+  <si>
+    <t>Defunciones registradas que permitan caracterizar el fenómeno de la mortalidad en el país.</t>
+  </si>
+  <si>
+    <t>Defunciones</t>
+  </si>
+  <si>
+    <t>INEGI. Estadísticas de Defunciones Registradas (EDR)</t>
+  </si>
+  <si>
+    <t>Eficiencia terminal Primaria (%)</t>
+  </si>
+  <si>
+    <t>Es el porcentaje de alumnos que concluyen un nivel educativo, respecto al número de alumnos que ingresaron a este nivel en la cohorte correspondiente.</t>
+  </si>
+  <si>
+    <t>Eficiencia terminal educación Secundaria (%)</t>
+  </si>
+  <si>
+    <t>Grado promedio de escolaridad (años)</t>
+  </si>
+  <si>
+    <t>Número de años que, en promedio, aprobaron las personas de 15 años y más, en el Sistema Educativo Nacional.</t>
+  </si>
+  <si>
+    <t>Años</t>
+  </si>
+  <si>
+    <t>Quinquenal</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población con Carencia por acceso a la alimentación nutritiva y de calidad</t>
+  </si>
+  <si>
+    <t>Población que se encuentra con carencia al acceso a la alimentación nutritiva y de calidad</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población con Carencia por acceso a la seguridad social</t>
+  </si>
+  <si>
+    <t>Población que se encuentra con carencia a la seguridad social</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población con Carencia por acceso a los servicios básicos en la vivienda</t>
+  </si>
+  <si>
+    <t>Población que se encuentra con carencia a los accesos de servicios básicos en la vievienda</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población con Carencia por acceso a los servicios de salud</t>
+  </si>
+  <si>
+    <t>Población que se encuentra con carencia a los servicios de salud</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población con Carencia por calidad y espacios de la vivienda</t>
+  </si>
+  <si>
+    <t>Población que se encuentra con carencia por calidad y espacios de la vivienda</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población con Población con Ingreso Inferior a la Línea de pobreza extrema por ingresos</t>
+  </si>
+  <si>
+    <t>Población con Ingreso Inferior a la Línea de pobreza extrema por ingresos</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población con Población con Ingreso Inferior a la Línea de pobreza por ingresos</t>
+  </si>
+  <si>
+    <t>Población con Ingreso Inferior a la Línea de pobreza por ingresos</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población con Rezago Educativo</t>
+  </si>
+  <si>
+    <t>Población que se encuentracon rezago educativo</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población en situación de Pobreza</t>
+  </si>
+  <si>
+    <t>Población que se encuentra en situación de pobreza</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Población en situación de Pobreza Moderada</t>
+  </si>
+  <si>
+    <t>Población que se encuentra en situación de pobreza moderada</t>
+  </si>
+  <si>
+    <t>Porcentaje de la Poblaciónn en situación de Pobreza Extrema</t>
+  </si>
+  <si>
+    <t>Población que se encuentra en situación de pobreza extrema</t>
+  </si>
+  <si>
+    <t>Porcentaje de la población vulnerable por ingresos</t>
+  </si>
+  <si>
+    <t>Población que se encuentra en situación de vulnerabilidad por ingresos</t>
+  </si>
+  <si>
+    <t>Tasa de Abandono Escolar Media Superior (%)</t>
+  </si>
+  <si>
+    <t>Tasa de Abandono escolar Educación Primaria (%)</t>
+  </si>
+  <si>
+    <t>Tasa de ocupación infantil no permitida</t>
+  </si>
+  <si>
+    <t>La ocupación infantil no permitida incluye trabajos que por ley no deben realizar menores de 18 años, ya que ponen en riesgo su salud, seguridad o desarrollo integral.</t>
+  </si>
+  <si>
+    <t>Trianual</t>
+  </si>
+  <si>
+    <t>INEGI. Encuesta Nacional de Trabajo Infantil (ENTI)</t>
+  </si>
+  <si>
+    <t>Tasa de quehaceres domésticos en condiciones no adecuadas</t>
+  </si>
+  <si>
+    <t>Son actividades no remuneradas dentro del hogar que afectan la salud o integridad de quienes las realizan, ya sea por ser peligrosas o por extenderse a horarios prolongados</t>
+  </si>
+  <si>
+    <t>Si_1000</t>
+  </si>
+  <si>
+    <t>Si_100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1182,13 +1211,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1470,11 +1509,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K159"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1500,7 +1539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1526,7 +1565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1552,7 +1591,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1578,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1604,7 +1643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1630,7 +1669,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1656,7 +1695,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1682,7 +1721,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1708,7 +1747,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1734,7 +1773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1760,7 +1799,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1786,7 +1825,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1812,7 +1851,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1838,7 +1877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1864,7 +1903,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -1890,7 +1929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1916,7 +1955,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -1942,7 +1981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1968,7 +2007,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1994,7 +2033,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2020,7 +2059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2046,7 +2085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -2072,7 +2111,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -2098,7 +2137,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -2124,7 +2163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -2150,7 +2189,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -2176,7 +2215,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -2202,7 +2241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -2228,7 +2267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -2254,7 +2293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -2280,7 +2319,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -2306,7 +2345,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -2332,7 +2371,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -2358,7 +2397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -2384,7 +2423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -2410,7 +2449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -2436,7 +2475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -2462,7 +2501,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -2488,7 +2527,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -2514,7 +2553,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -2540,7 +2579,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -2566,7 +2605,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -2592,7 +2631,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -2618,7 +2657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -2644,7 +2683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -2670,7 +2709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -2696,7 +2735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -2722,7 +2761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -2748,7 +2787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -2774,7 +2813,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -2800,7 +2839,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -2826,7 +2865,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2852,7 +2891,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2878,7 +2917,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2904,7 +2943,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -2930,7 +2969,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -2956,7 +2995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2982,7 +3021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -3008,7 +3047,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -3034,7 +3073,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -3048,7 +3087,7 @@
         <v>146</v>
       </c>
       <c r="E61" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
       <c r="F61" t="s">
         <v>41</v>
@@ -3056,23 +3095,22 @@
       <c r="G61" t="s">
         <v>26</v>
       </c>
-      <c r="H61"/>
-    </row>
-    <row r="62">
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>8</v>
       </c>
       <c r="B62" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62" t="s">
         <v>148</v>
-      </c>
-      <c r="C62" t="s">
-        <v>149</v>
       </c>
       <c r="D62" t="s">
         <v>146</v>
       </c>
       <c r="E62" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
@@ -3081,24 +3119,24 @@
         <v>26</v>
       </c>
       <c r="H62" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>8</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>151</v>
-      </c>
-      <c r="C63" t="s">
-        <v>152</v>
       </c>
       <c r="D63" t="s">
         <v>146</v>
       </c>
       <c r="E63" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
@@ -3106,17 +3144,16 @@
       <c r="G63" t="s">
         <v>26</v>
       </c>
-      <c r="H63"/>
-    </row>
-    <row r="64">
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>8</v>
       </c>
       <c r="B64" t="s">
+        <v>152</v>
+      </c>
+      <c r="C64" t="s">
         <v>153</v>
-      </c>
-      <c r="C64" t="s">
-        <v>154</v>
       </c>
       <c r="D64" t="s">
         <v>44</v>
@@ -3134,15 +3171,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>8</v>
       </c>
       <c r="B65" t="s">
+        <v>154</v>
+      </c>
+      <c r="C65" t="s">
         <v>155</v>
-      </c>
-      <c r="C65" t="s">
-        <v>156</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -3157,20 +3194,19 @@
         <v>14</v>
       </c>
       <c r="H65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>158</v>
       </c>
-      <c r="C66" t="s">
-        <v>159</v>
-      </c>
-      <c r="D66"/>
       <c r="E66" t="s">
         <v>12</v>
       </c>
@@ -3184,91 +3220,90 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>8</v>
       </c>
       <c r="B67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" t="s">
         <v>160</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>161</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" t="s">
         <v>162</v>
       </c>
-      <c r="E67" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>163</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>164</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" t="s">
         <v>165</v>
       </c>
-      <c r="E68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" t="s">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>8</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>167</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
+        <v>164</v>
+      </c>
+      <c r="E69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" t="s">
         <v>168</v>
       </c>
-      <c r="D69" t="s">
-        <v>165</v>
-      </c>
-      <c r="E69" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>8</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>169</v>
-      </c>
-      <c r="C70" t="s">
-        <v>170</v>
       </c>
       <c r="D70" t="s">
         <v>97</v>
@@ -3282,17 +3317,16 @@
       <c r="G70" t="s">
         <v>26</v>
       </c>
-      <c r="H70"/>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>8</v>
       </c>
       <c r="B71" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" t="s">
         <v>171</v>
-      </c>
-      <c r="C71" t="s">
-        <v>172</v>
       </c>
       <c r="D71" t="s">
         <v>97</v>
@@ -3306,17 +3340,16 @@
       <c r="G71" t="s">
         <v>26</v>
       </c>
-      <c r="H71"/>
-    </row>
-    <row r="72">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>8</v>
       </c>
       <c r="B72" t="s">
+        <v>172</v>
+      </c>
+      <c r="C72" t="s">
         <v>173</v>
-      </c>
-      <c r="C72" t="s">
-        <v>174</v>
       </c>
       <c r="D72" t="s">
         <v>97</v>
@@ -3330,17 +3363,17 @@
       <c r="G72" t="s">
         <v>26</v>
       </c>
-      <c r="H72"/>
-    </row>
-    <row r="73">
+      <c r="K72" s="1"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>8</v>
       </c>
       <c r="B73" t="s">
+        <v>174</v>
+      </c>
+      <c r="C73" t="s">
         <v>175</v>
-      </c>
-      <c r="C73" t="s">
-        <v>176</v>
       </c>
       <c r="D73" t="s">
         <v>97</v>
@@ -3354,17 +3387,16 @@
       <c r="G73" t="s">
         <v>26</v>
       </c>
-      <c r="H73"/>
-    </row>
-    <row r="74">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>8</v>
       </c>
       <c r="B74" t="s">
+        <v>176</v>
+      </c>
+      <c r="C74" t="s">
         <v>177</v>
-      </c>
-      <c r="C74" t="s">
-        <v>178</v>
       </c>
       <c r="D74" t="s">
         <v>97</v>
@@ -3378,17 +3410,16 @@
       <c r="G74" t="s">
         <v>26</v>
       </c>
-      <c r="H74"/>
-    </row>
-    <row r="75">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>8</v>
       </c>
       <c r="B75" t="s">
+        <v>178</v>
+      </c>
+      <c r="C75" t="s">
         <v>179</v>
-      </c>
-      <c r="C75" t="s">
-        <v>180</v>
       </c>
       <c r="D75" t="s">
         <v>97</v>
@@ -3402,17 +3433,16 @@
       <c r="G75" t="s">
         <v>26</v>
       </c>
-      <c r="H75"/>
-    </row>
-    <row r="76">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>8</v>
       </c>
       <c r="B76" t="s">
+        <v>180</v>
+      </c>
+      <c r="C76" t="s">
         <v>181</v>
-      </c>
-      <c r="C76" t="s">
-        <v>182</v>
       </c>
       <c r="D76" t="s">
         <v>97</v>
@@ -3426,17 +3456,16 @@
       <c r="G76" t="s">
         <v>26</v>
       </c>
-      <c r="H76"/>
-    </row>
-    <row r="77">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>8</v>
       </c>
       <c r="B77" t="s">
+        <v>182</v>
+      </c>
+      <c r="C77" t="s">
         <v>183</v>
-      </c>
-      <c r="C77" t="s">
-        <v>184</v>
       </c>
       <c r="D77" t="s">
         <v>97</v>
@@ -3450,17 +3479,16 @@
       <c r="G77" t="s">
         <v>26</v>
       </c>
-      <c r="H77"/>
-    </row>
-    <row r="78">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>8</v>
       </c>
       <c r="B78" t="s">
+        <v>184</v>
+      </c>
+      <c r="C78" t="s">
         <v>185</v>
-      </c>
-      <c r="C78" t="s">
-        <v>186</v>
       </c>
       <c r="D78" t="s">
         <v>97</v>
@@ -3474,23 +3502,22 @@
       <c r="G78" t="s">
         <v>26</v>
       </c>
-      <c r="H78"/>
-    </row>
-    <row r="79">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>8</v>
       </c>
       <c r="B79" t="s">
+        <v>186</v>
+      </c>
+      <c r="C79" t="s">
         <v>187</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>188</v>
       </c>
-      <c r="D79" t="s">
-        <v>189</v>
-      </c>
       <c r="E79" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
       <c r="F79" t="s">
         <v>13</v>
@@ -3499,18 +3526,18 @@
         <v>48</v>
       </c>
       <c r="H79" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>8</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>191</v>
-      </c>
-      <c r="C80" t="s">
-        <v>192</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
@@ -3525,44 +3552,44 @@
         <v>14</v>
       </c>
       <c r="H80" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>8</v>
       </c>
       <c r="B81" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81" t="s">
         <v>193</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>194</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" t="s">
         <v>195</v>
       </c>
-      <c r="E81" t="s">
-        <v>12</v>
-      </c>
-      <c r="F81" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>8</v>
-      </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>196</v>
-      </c>
-      <c r="C82" t="s">
-        <v>197</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -3577,44 +3604,44 @@
         <v>14</v>
       </c>
       <c r="H82" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>8</v>
       </c>
       <c r="B83" t="s">
+        <v>197</v>
+      </c>
+      <c r="C83" t="s">
         <v>198</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>199</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" t="s">
         <v>200</v>
       </c>
-      <c r="E83" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" t="s">
-        <v>14</v>
-      </c>
-      <c r="H83" t="s">
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>202</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>203</v>
-      </c>
-      <c r="C84" t="s">
-        <v>204</v>
       </c>
       <c r="D84" t="s">
         <v>44</v>
@@ -3629,18 +3656,18 @@
         <v>14</v>
       </c>
       <c r="H84" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>201</v>
+      </c>
+      <c r="B85" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>202</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>206</v>
-      </c>
-      <c r="C85" t="s">
-        <v>207</v>
       </c>
       <c r="D85" t="s">
         <v>44</v>
@@ -3655,18 +3682,18 @@
         <v>80</v>
       </c>
       <c r="H85" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>201</v>
+      </c>
+      <c r="B86" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>202</v>
-      </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>209</v>
-      </c>
-      <c r="C86" t="s">
-        <v>210</v>
       </c>
       <c r="D86" t="s">
         <v>44</v>
@@ -3681,18 +3708,18 @@
         <v>80</v>
       </c>
       <c r="H86" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B87" t="s">
+        <v>210</v>
+      </c>
+      <c r="C87" t="s">
         <v>211</v>
-      </c>
-      <c r="C87" t="s">
-        <v>212</v>
       </c>
       <c r="D87" t="s">
         <v>97</v>
@@ -3707,18 +3734,18 @@
         <v>80</v>
       </c>
       <c r="H87" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B88" t="s">
+        <v>212</v>
+      </c>
+      <c r="C88" t="s">
         <v>213</v>
-      </c>
-      <c r="C88" t="s">
-        <v>214</v>
       </c>
       <c r="D88" t="s">
         <v>97</v>
@@ -3733,18 +3760,18 @@
         <v>80</v>
       </c>
       <c r="H88" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>214</v>
+      </c>
+      <c r="B89" t="s">
         <v>215</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>216</v>
-      </c>
-      <c r="C89" t="s">
-        <v>217</v>
       </c>
       <c r="D89" t="s">
         <v>44</v>
@@ -3759,18 +3786,18 @@
         <v>14</v>
       </c>
       <c r="H89" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>214</v>
+      </c>
+      <c r="B90" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>215</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>219</v>
-      </c>
-      <c r="C90" t="s">
-        <v>220</v>
       </c>
       <c r="D90" t="s">
         <v>44</v>
@@ -3785,44 +3812,44 @@
         <v>14</v>
       </c>
       <c r="H90" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B91" t="s">
+        <v>220</v>
+      </c>
+      <c r="C91" t="s">
         <v>221</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>222</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
+        <v>377</v>
+      </c>
+      <c r="F91" t="s">
+        <v>41</v>
+      </c>
+      <c r="G91" t="s">
+        <v>14</v>
+      </c>
+      <c r="H91" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" t="s">
         <v>223</v>
       </c>
-      <c r="E91" t="s">
-        <v>147</v>
-      </c>
-      <c r="F91" t="s">
-        <v>41</v>
-      </c>
-      <c r="G91" t="s">
-        <v>14</v>
-      </c>
-      <c r="H91" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>215</v>
-      </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>224</v>
-      </c>
-      <c r="C92" t="s">
-        <v>225</v>
       </c>
       <c r="D92" t="s">
         <v>44</v>
@@ -3837,44 +3864,44 @@
         <v>14</v>
       </c>
       <c r="H92" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B93" t="s">
+        <v>225</v>
+      </c>
+      <c r="C93" t="s">
         <v>226</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>227</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H93" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>214</v>
+      </c>
+      <c r="B94" t="s">
         <v>228</v>
       </c>
-      <c r="E93" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" t="s">
-        <v>41</v>
-      </c>
-      <c r="G93" t="s">
-        <v>14</v>
-      </c>
-      <c r="H93" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>215</v>
-      </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>229</v>
-      </c>
-      <c r="C94" t="s">
-        <v>230</v>
       </c>
       <c r="D94" t="s">
         <v>44</v>
@@ -3889,18 +3916,18 @@
         <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B95" t="s">
+        <v>230</v>
+      </c>
+      <c r="C95" t="s">
         <v>231</v>
-      </c>
-      <c r="C95" t="s">
-        <v>232</v>
       </c>
       <c r="D95" t="s">
         <v>44</v>
@@ -3915,44 +3942,44 @@
         <v>14</v>
       </c>
       <c r="H95" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B96" t="s">
+        <v>232</v>
+      </c>
+      <c r="C96" t="s">
         <v>233</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>234</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>377</v>
+      </c>
+      <c r="F96" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" t="s">
+        <v>14</v>
+      </c>
+      <c r="H96" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" t="s">
         <v>235</v>
       </c>
-      <c r="E96" t="s">
-        <v>147</v>
-      </c>
-      <c r="F96" t="s">
-        <v>41</v>
-      </c>
-      <c r="G96" t="s">
-        <v>14</v>
-      </c>
-      <c r="H96" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>215</v>
-      </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>236</v>
-      </c>
-      <c r="C97" t="s">
-        <v>237</v>
       </c>
       <c r="D97" t="s">
         <v>44</v>
@@ -3967,18 +3994,18 @@
         <v>14</v>
       </c>
       <c r="H97" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B98" t="s">
+        <v>237</v>
+      </c>
+      <c r="C98" t="s">
         <v>238</v>
-      </c>
-      <c r="C98" t="s">
-        <v>239</v>
       </c>
       <c r="D98" t="s">
         <v>44</v>
@@ -3993,18 +4020,18 @@
         <v>14</v>
       </c>
       <c r="H98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B99" t="s">
+        <v>239</v>
+      </c>
+      <c r="C99" t="s">
         <v>240</v>
-      </c>
-      <c r="C99" t="s">
-        <v>241</v>
       </c>
       <c r="D99" t="s">
         <v>44</v>
@@ -4019,18 +4046,18 @@
         <v>14</v>
       </c>
       <c r="H99" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B100" t="s">
+        <v>241</v>
+      </c>
+      <c r="C100" t="s">
         <v>242</v>
-      </c>
-      <c r="C100" t="s">
-        <v>243</v>
       </c>
       <c r="D100" t="s">
         <v>44</v>
@@ -4045,18 +4072,18 @@
         <v>14</v>
       </c>
       <c r="H100" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B101" t="s">
+        <v>243</v>
+      </c>
+      <c r="C101" t="s">
         <v>244</v>
-      </c>
-      <c r="C101" t="s">
-        <v>245</v>
       </c>
       <c r="D101" t="s">
         <v>44</v>
@@ -4071,18 +4098,18 @@
         <v>14</v>
       </c>
       <c r="H101" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B102" t="s">
+        <v>245</v>
+      </c>
+      <c r="C102" t="s">
         <v>246</v>
-      </c>
-      <c r="C102" t="s">
-        <v>247</v>
       </c>
       <c r="D102" t="s">
         <v>44</v>
@@ -4097,44 +4124,44 @@
         <v>14</v>
       </c>
       <c r="H102" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B103" t="s">
+        <v>247</v>
+      </c>
+      <c r="C103" t="s">
         <v>248</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>249</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" t="s">
+        <v>14</v>
+      </c>
+      <c r="H103" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>214</v>
+      </c>
+      <c r="B104" t="s">
         <v>250</v>
       </c>
-      <c r="E103" t="s">
-        <v>12</v>
-      </c>
-      <c r="F103" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" t="s">
-        <v>14</v>
-      </c>
-      <c r="H103" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>215</v>
-      </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>251</v>
-      </c>
-      <c r="C104" t="s">
-        <v>252</v>
       </c>
       <c r="D104" t="s">
         <v>44</v>
@@ -4149,44 +4176,44 @@
         <v>14</v>
       </c>
       <c r="H104" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="105">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B105" t="s">
+        <v>252</v>
+      </c>
+      <c r="C105" t="s">
         <v>253</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>254</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
+        <v>377</v>
+      </c>
+      <c r="F105" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" t="s">
+        <v>14</v>
+      </c>
+      <c r="H105" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>214</v>
+      </c>
+      <c r="B106" t="s">
         <v>255</v>
       </c>
-      <c r="E105" t="s">
-        <v>147</v>
-      </c>
-      <c r="F105" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" t="s">
-        <v>14</v>
-      </c>
-      <c r="H105" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>215</v>
-      </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>256</v>
-      </c>
-      <c r="C106" t="s">
-        <v>257</v>
       </c>
       <c r="D106" t="s">
         <v>44</v>
@@ -4201,18 +4228,18 @@
         <v>14</v>
       </c>
       <c r="H106" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B107" t="s">
+        <v>257</v>
+      </c>
+      <c r="C107" t="s">
         <v>258</v>
-      </c>
-      <c r="C107" t="s">
-        <v>259</v>
       </c>
       <c r="D107" t="s">
         <v>44</v>
@@ -4227,122 +4254,122 @@
         <v>14</v>
       </c>
       <c r="H107" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>259</v>
+      </c>
+      <c r="B108" t="s">
         <v>260</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>261</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
+        <v>164</v>
+      </c>
+      <c r="E108" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" t="s">
+        <v>14</v>
+      </c>
+      <c r="H108" t="s">
         <v>262</v>
       </c>
-      <c r="D108" t="s">
-        <v>165</v>
-      </c>
-      <c r="E108" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" t="s">
-        <v>14</v>
-      </c>
-      <c r="H108" t="s">
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>259</v>
+      </c>
+      <c r="B109" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>260</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>264</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>265</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109" t="s">
         <v>266</v>
       </c>
-      <c r="E109" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" t="s">
-        <v>14</v>
-      </c>
-      <c r="H109" t="s">
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>259</v>
+      </c>
+      <c r="B110" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>260</v>
-      </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>268</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>269</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" t="s">
+        <v>14</v>
+      </c>
+      <c r="H110" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>259</v>
+      </c>
+      <c r="B111" t="s">
         <v>270</v>
       </c>
-      <c r="E110" t="s">
-        <v>12</v>
-      </c>
-      <c r="F110" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>260</v>
-      </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>271</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>272</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" t="s">
+        <v>14</v>
+      </c>
+      <c r="H111" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>273</v>
       </c>
-      <c r="E111" t="s">
-        <v>12</v>
-      </c>
-      <c r="F111" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" t="s">
-        <v>14</v>
-      </c>
-      <c r="H111" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
         <v>274</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>275</v>
-      </c>
-      <c r="C112" t="s">
-        <v>276</v>
       </c>
       <c r="D112" t="s">
         <v>44</v>
@@ -4357,18 +4384,18 @@
         <v>14</v>
       </c>
       <c r="H112" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>273</v>
+      </c>
+      <c r="B113" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>274</v>
-      </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>278</v>
-      </c>
-      <c r="C113" t="s">
-        <v>279</v>
       </c>
       <c r="D113" t="s">
         <v>44</v>
@@ -4383,24 +4410,24 @@
         <v>14</v>
       </c>
       <c r="H113" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B114" t="s">
+        <v>279</v>
+      </c>
+      <c r="C114" t="s">
         <v>280</v>
       </c>
-      <c r="C114" t="s">
-        <v>281</v>
-      </c>
       <c r="D114" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E114" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F114" t="s">
         <v>41</v>
@@ -4409,24 +4436,24 @@
         <v>48</v>
       </c>
       <c r="H114" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>273</v>
+      </c>
+      <c r="B115" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>274</v>
-      </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>283</v>
       </c>
-      <c r="C115" t="s">
-        <v>284</v>
-      </c>
       <c r="D115" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E115" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F115" t="s">
         <v>41</v>
@@ -4435,24 +4462,24 @@
         <v>48</v>
       </c>
       <c r="H115" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B116" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C116" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D116" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E116" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F116" t="s">
         <v>41</v>
@@ -4461,24 +4488,24 @@
         <v>48</v>
       </c>
       <c r="H116" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B117" t="s">
+        <v>285</v>
+      </c>
+      <c r="C117" t="s">
         <v>286</v>
       </c>
-      <c r="C117" t="s">
-        <v>287</v>
-      </c>
       <c r="D117" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E117" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F117" t="s">
         <v>41</v>
@@ -4487,50 +4514,50 @@
         <v>48</v>
       </c>
       <c r="H117" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="118">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B118" t="s">
+        <v>287</v>
+      </c>
+      <c r="C118" t="s">
         <v>288</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>199</v>
+      </c>
+      <c r="E118" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118" t="s">
         <v>289</v>
       </c>
-      <c r="D118" t="s">
-        <v>200</v>
-      </c>
-      <c r="E118" t="s">
-        <v>12</v>
-      </c>
-      <c r="F118" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" t="s">
-        <v>14</v>
-      </c>
-      <c r="H118" t="s">
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>273</v>
+      </c>
+      <c r="B119" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>274</v>
-      </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>291</v>
       </c>
-      <c r="C119" t="s">
-        <v>292</v>
-      </c>
       <c r="D119" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E119" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F119" t="s">
         <v>41</v>
@@ -4539,24 +4566,24 @@
         <v>48</v>
       </c>
       <c r="H119" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B120" t="s">
+        <v>292</v>
+      </c>
+      <c r="C120" t="s">
         <v>293</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>294</v>
       </c>
-      <c r="D120" t="s">
-        <v>295</v>
-      </c>
       <c r="E120" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F120" t="s">
         <v>41</v>
@@ -4568,21 +4595,21 @@
         <v>60</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B121" t="s">
+        <v>295</v>
+      </c>
+      <c r="C121" t="s">
         <v>296</v>
       </c>
-      <c r="C121" t="s">
-        <v>297</v>
-      </c>
       <c r="D121" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E121" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F121" t="s">
         <v>41</v>
@@ -4591,21 +4618,21 @@
         <v>48</v>
       </c>
       <c r="H121" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B122" t="s">
+        <v>297</v>
+      </c>
+      <c r="C122" t="s">
         <v>298</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>299</v>
-      </c>
-      <c r="D122" t="s">
-        <v>300</v>
       </c>
       <c r="E122" t="s">
         <v>12</v>
@@ -4620,15 +4647,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B123" t="s">
+        <v>300</v>
+      </c>
+      <c r="C123" t="s">
         <v>301</v>
-      </c>
-      <c r="C123" t="s">
-        <v>302</v>
       </c>
       <c r="D123" t="s">
         <v>44</v>
@@ -4643,18 +4670,18 @@
         <v>14</v>
       </c>
       <c r="H123" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B124" t="s">
+        <v>302</v>
+      </c>
+      <c r="C124" t="s">
         <v>303</v>
-      </c>
-      <c r="C124" t="s">
-        <v>304</v>
       </c>
       <c r="D124" t="s">
         <v>44</v>
@@ -4669,18 +4696,18 @@
         <v>14</v>
       </c>
       <c r="H124" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="125">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B125" t="s">
+        <v>304</v>
+      </c>
+      <c r="C125" t="s">
         <v>305</v>
-      </c>
-      <c r="C125" t="s">
-        <v>306</v>
       </c>
       <c r="D125" t="s">
         <v>44</v>
@@ -4695,24 +4722,24 @@
         <v>14</v>
       </c>
       <c r="H125" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B126" t="s">
+        <v>306</v>
+      </c>
+      <c r="C126" t="s">
         <v>307</v>
       </c>
-      <c r="C126" t="s">
-        <v>308</v>
-      </c>
       <c r="D126" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E126" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F126" t="s">
         <v>41</v>
@@ -4721,24 +4748,24 @@
         <v>48</v>
       </c>
       <c r="H126" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B127" t="s">
+        <v>308</v>
+      </c>
+      <c r="C127" t="s">
         <v>309</v>
       </c>
-      <c r="C127" t="s">
-        <v>310</v>
-      </c>
       <c r="D127" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E127" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F127" t="s">
         <v>41</v>
@@ -4747,24 +4774,24 @@
         <v>48</v>
       </c>
       <c r="H127" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="128">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B128" t="s">
+        <v>310</v>
+      </c>
+      <c r="C128" t="s">
         <v>311</v>
       </c>
-      <c r="C128" t="s">
-        <v>312</v>
-      </c>
       <c r="D128" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E128" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F128" t="s">
         <v>41</v>
@@ -4773,24 +4800,24 @@
         <v>48</v>
       </c>
       <c r="H128" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B129" t="s">
+        <v>312</v>
+      </c>
+      <c r="C129" t="s">
         <v>313</v>
       </c>
-      <c r="C129" t="s">
-        <v>314</v>
-      </c>
       <c r="D129" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E129" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F129" t="s">
         <v>41</v>
@@ -4799,18 +4826,18 @@
         <v>48</v>
       </c>
       <c r="H129" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="130">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B130" t="s">
+        <v>314</v>
+      </c>
+      <c r="C130" t="s">
         <v>315</v>
-      </c>
-      <c r="C130" t="s">
-        <v>316</v>
       </c>
       <c r="D130" t="s">
         <v>97</v>
@@ -4825,18 +4852,18 @@
         <v>14</v>
       </c>
       <c r="H130" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="131">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B131" t="s">
+        <v>316</v>
+      </c>
+      <c r="C131" t="s">
         <v>317</v>
-      </c>
-      <c r="C131" t="s">
-        <v>318</v>
       </c>
       <c r="D131" t="s">
         <v>97</v>
@@ -4851,18 +4878,18 @@
         <v>14</v>
       </c>
       <c r="H131" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="132">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B132" t="s">
+        <v>318</v>
+      </c>
+      <c r="C132" t="s">
         <v>319</v>
-      </c>
-      <c r="C132" t="s">
-        <v>320</v>
       </c>
       <c r="D132" t="s">
         <v>97</v>
@@ -4877,24 +4904,24 @@
         <v>14</v>
       </c>
       <c r="H132" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="133">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B133" t="s">
+        <v>320</v>
+      </c>
+      <c r="C133" t="s">
         <v>321</v>
       </c>
-      <c r="C133" t="s">
-        <v>322</v>
-      </c>
       <c r="D133" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E133" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F133" t="s">
         <v>41</v>
@@ -4903,24 +4930,24 @@
         <v>48</v>
       </c>
       <c r="H133" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="134">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B134" t="s">
+        <v>322</v>
+      </c>
+      <c r="C134" t="s">
         <v>323</v>
       </c>
-      <c r="C134" t="s">
-        <v>324</v>
-      </c>
       <c r="D134" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E134" t="s">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c r="F134" t="s">
         <v>41</v>
@@ -4929,18 +4956,18 @@
         <v>48</v>
       </c>
       <c r="H134" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="135">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>324</v>
+      </c>
+      <c r="B135" t="s">
         <v>325</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>326</v>
-      </c>
-      <c r="C135" t="s">
-        <v>327</v>
       </c>
       <c r="D135" t="s">
         <v>44</v>
@@ -4955,18 +4982,18 @@
         <v>14</v>
       </c>
       <c r="H135" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>324</v>
+      </c>
+      <c r="B136" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>325</v>
-      </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>329</v>
-      </c>
-      <c r="C136" t="s">
-        <v>330</v>
       </c>
       <c r="D136" t="s">
         <v>44</v>
@@ -4981,18 +5008,18 @@
         <v>14</v>
       </c>
       <c r="H136" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="137">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B137" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C137" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D137" t="s">
         <v>44</v>
@@ -5007,18 +5034,18 @@
         <v>14</v>
       </c>
       <c r="H137" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="138">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B138" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C138" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D138" t="s">
         <v>44</v>
@@ -5033,18 +5060,18 @@
         <v>14</v>
       </c>
       <c r="H138" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="139">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B139" t="s">
+        <v>332</v>
+      </c>
+      <c r="C139" t="s">
         <v>333</v>
-      </c>
-      <c r="C139" t="s">
-        <v>334</v>
       </c>
       <c r="D139" t="s">
         <v>44</v>
@@ -5059,44 +5086,44 @@
         <v>14</v>
       </c>
       <c r="H139" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="140">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B140" t="s">
+        <v>334</v>
+      </c>
+      <c r="C140" t="s">
         <v>335</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>336</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" t="s">
+        <v>41</v>
+      </c>
+      <c r="G140" t="s">
+        <v>14</v>
+      </c>
+      <c r="H140" t="s">
         <v>337</v>
       </c>
-      <c r="E140" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" t="s">
-        <v>41</v>
-      </c>
-      <c r="G140" t="s">
-        <v>14</v>
-      </c>
-      <c r="H140" t="s">
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>324</v>
+      </c>
+      <c r="B141" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>325</v>
-      </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
         <v>339</v>
-      </c>
-      <c r="C141" t="s">
-        <v>340</v>
       </c>
       <c r="D141" t="s">
         <v>44</v>
@@ -5111,18 +5138,18 @@
         <v>14</v>
       </c>
       <c r="H141" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="142">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B142" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C142" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D142" t="s">
         <v>44</v>
@@ -5137,44 +5164,44 @@
         <v>14</v>
       </c>
       <c r="H142" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="143">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B143" t="s">
+        <v>341</v>
+      </c>
+      <c r="C143" t="s">
         <v>342</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
         <v>343</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143" t="s">
         <v>344</v>
-      </c>
-      <c r="E143" t="s">
-        <v>12</v>
-      </c>
-      <c r="F143" t="s">
-        <v>13</v>
-      </c>
-      <c r="G143" t="s">
-        <v>345</v>
       </c>
       <c r="H143" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B144" t="s">
+        <v>345</v>
+      </c>
+      <c r="C144" t="s">
         <v>346</v>
-      </c>
-      <c r="C144" t="s">
-        <v>347</v>
       </c>
       <c r="D144" t="s">
         <v>44</v>
@@ -5192,15 +5219,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B145" t="s">
+        <v>347</v>
+      </c>
+      <c r="C145" t="s">
         <v>348</v>
-      </c>
-      <c r="C145" t="s">
-        <v>349</v>
       </c>
       <c r="D145" t="s">
         <v>44</v>
@@ -5218,15 +5245,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B146" t="s">
+        <v>349</v>
+      </c>
+      <c r="C146" t="s">
         <v>350</v>
-      </c>
-      <c r="C146" t="s">
-        <v>351</v>
       </c>
       <c r="D146" t="s">
         <v>44</v>
@@ -5244,15 +5271,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B147" t="s">
+        <v>351</v>
+      </c>
+      <c r="C147" t="s">
         <v>352</v>
-      </c>
-      <c r="C147" t="s">
-        <v>353</v>
       </c>
       <c r="D147" t="s">
         <v>44</v>
@@ -5270,15 +5297,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B148" t="s">
+        <v>353</v>
+      </c>
+      <c r="C148" t="s">
         <v>354</v>
-      </c>
-      <c r="C148" t="s">
-        <v>355</v>
       </c>
       <c r="D148" t="s">
         <v>44</v>
@@ -5296,15 +5323,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B149" t="s">
+        <v>355</v>
+      </c>
+      <c r="C149" t="s">
         <v>356</v>
-      </c>
-      <c r="C149" t="s">
-        <v>357</v>
       </c>
       <c r="D149" t="s">
         <v>44</v>
@@ -5322,15 +5349,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B150" t="s">
+        <v>357</v>
+      </c>
+      <c r="C150" t="s">
         <v>358</v>
-      </c>
-      <c r="C150" t="s">
-        <v>359</v>
       </c>
       <c r="D150" t="s">
         <v>44</v>
@@ -5348,15 +5375,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B151" t="s">
+        <v>359</v>
+      </c>
+      <c r="C151" t="s">
         <v>360</v>
-      </c>
-      <c r="C151" t="s">
-        <v>361</v>
       </c>
       <c r="D151" t="s">
         <v>44</v>
@@ -5374,15 +5401,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B152" t="s">
+        <v>361</v>
+      </c>
+      <c r="C152" t="s">
         <v>362</v>
-      </c>
-      <c r="C152" t="s">
-        <v>363</v>
       </c>
       <c r="D152" t="s">
         <v>44</v>
@@ -5400,15 +5427,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B153" t="s">
+        <v>363</v>
+      </c>
+      <c r="C153" t="s">
         <v>364</v>
-      </c>
-      <c r="C153" t="s">
-        <v>365</v>
       </c>
       <c r="D153" t="s">
         <v>44</v>
@@ -5426,15 +5453,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B154" t="s">
+        <v>365</v>
+      </c>
+      <c r="C154" t="s">
         <v>366</v>
-      </c>
-      <c r="C154" t="s">
-        <v>367</v>
       </c>
       <c r="D154" t="s">
         <v>44</v>
@@ -5452,15 +5479,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B155" t="s">
+        <v>367</v>
+      </c>
+      <c r="C155" t="s">
         <v>368</v>
-      </c>
-      <c r="C155" t="s">
-        <v>369</v>
       </c>
       <c r="D155" t="s">
         <v>44</v>
@@ -5478,15 +5505,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B156" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C156" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D156" t="s">
         <v>44</v>
@@ -5501,18 +5528,18 @@
         <v>14</v>
       </c>
       <c r="H156" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="157">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B157" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C157" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D157" t="s">
         <v>44</v>
@@ -5527,47 +5554,47 @@
         <v>14</v>
       </c>
       <c r="H157" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="158">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B158" t="s">
+        <v>371</v>
+      </c>
+      <c r="C158" t="s">
         <v>372</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
+        <v>249</v>
+      </c>
+      <c r="E158" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" t="s">
+        <v>41</v>
+      </c>
+      <c r="G158" t="s">
         <v>373</v>
       </c>
-      <c r="D158" t="s">
-        <v>250</v>
-      </c>
-      <c r="E158" t="s">
-        <v>12</v>
-      </c>
-      <c r="F158" t="s">
-        <v>41</v>
-      </c>
-      <c r="G158" t="s">
+      <c r="H158" t="s">
         <v>374</v>
       </c>
-      <c r="H158" t="s">
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>324</v>
+      </c>
+      <c r="B159" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>325</v>
-      </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>376</v>
       </c>
-      <c r="C159" t="s">
-        <v>377</v>
-      </c>
       <c r="D159" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E159" t="s">
         <v>12</v>
@@ -5576,14 +5603,15 @@
         <v>41</v>
       </c>
       <c r="G159" t="s">
+        <v>373</v>
+      </c>
+      <c r="H159" t="s">
         <v>374</v>
       </c>
-      <c r="H159" t="s">
-        <v>375</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>